--- a/data/processed/NACA_0012.xlsx
+++ b/data/processed/NACA_0012.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/af2385_bath_ac_uk/Documents/Desktop/CFD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/af2385_bath_ac_uk/Documents/Desktop/CFD/naca0012-cfd-validation/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4A9EFCD-C187-4135-9310-40957FEE2944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{C4A9EFCD-C187-4135-9310-40957FEE2944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AAAC8B1-26C5-4EAA-A63B-FD2AE8CC0222}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3E7BB595-B60C-434F-B89E-BE5A2F49B2D6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{3E7BB595-B60C-434F-B89E-BE5A2F49B2D6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="xflr5 data" sheetId="1" r:id="rId1"/>
+    <sheet name="comparison" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>alpha</t>
   </si>
@@ -70,13 +71,82 @@
   <si>
     <t>Gradient of lift coefficient for every degree increase in alpha</t>
   </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>XFOIL</t>
+  </si>
+  <si>
+    <t>Corrected</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Lift slope, α = 0–8°</t>
+  </si>
+  <si>
+    <t>0.10966 /deg</t>
+  </si>
+  <si>
+    <t>Thin aerofoil theory, 2π/rad</t>
+  </si>
+  <si>
+    <t>Cl at α = 10°</t>
+  </si>
+  <si>
+    <t>NASA TMR SA, 7-code mean</t>
+  </si>
+  <si>
+    <t>Cl at α = 15°</t>
+  </si>
+  <si>
+    <t>Cd at α = 0°</t>
+  </si>
+  <si>
+    <t>Cd at α = 10°</t>
+  </si>
+  <si>
+    <t>Cd at α = 15°</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>XFOIL runs free transition; the NASA SA reference is fully turbulent. Lift is higher and drag lower as a result.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -101,14 +171,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -121,6 +203,1225 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>NACA 0012 drag polar — XFOIL, Re = 6×10⁶, M = 0, free transition</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'xflr5 data'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'xflr5 data'!$B$2:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.6500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.22570000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.28179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.3377</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.39360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44929999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.50490000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.56030000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.61560000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.67049999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.72470000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.77849999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.83150000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.88400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.94020000000000004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.99890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0612999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.1222000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.1828000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.2273000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.2728999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.32</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3689</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.4174</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.4645999999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.51</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.5532999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.5942000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'xflr5 data'!$C$2:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.0699999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0800000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.1399999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2100000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3099999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4400000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.5999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.77E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.94E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.1500000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3499999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5500000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.79E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.0600000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.3400000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.6400000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.3700000000000007E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.7899999999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.2200000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.7699999999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.022E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.0670000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.123E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.188E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.2409999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.298E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.363E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.438E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.525E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.6209999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FFAF-4506-9698-2185391EEBBB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1622669743"/>
+        <c:axId val="268699183"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1622669743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Cl</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="268699183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="268699183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Cd</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1622669743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>365125</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>60325</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59E8BB20-88FF-1C56-D6D0-F56F5EDD82A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1668,5 +2969,182 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228D5D5E-AB56-449B-996C-7E83C8478A35}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" customWidth="1"/>
+    <col min="3" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <f>SLOPE('xflr5 data'!B2:B18,'xflr5 data'!A2:A18)</f>
+        <v>0.11080441176470587</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3">
+        <f>(B2-0.10966)/0.10966</f>
+        <v>1.0436000042913368E-2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <f>'xflr5 data'!B22</f>
+        <v>1.1222000000000001</v>
+      </c>
+      <c r="C3">
+        <f>B3/SQRT(1-0.15^2)</f>
+        <v>1.1350418674748153</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.0934999999999999</v>
+      </c>
+      <c r="E3" s="3">
+        <f>(C3-D3)/D3</f>
+        <v>3.7989819364257306E-2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <f>'xflr5 data'!B32</f>
+        <v>1.5942000000000001</v>
+      </c>
+      <c r="C4">
+        <f>B4/SQRT(1-0.15^2)</f>
+        <v>1.612443187603235</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.5518000000000001</v>
+      </c>
+      <c r="E4" s="3">
+        <f>(C4-D4)/D4</f>
+        <v>3.9079254802961046E-2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <f>'xflr5 data'!C2</f>
+        <v>5.0699999999999999E-3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8.1700000000000002E-3</v>
+      </c>
+      <c r="E5" s="3">
+        <f>(B5-D5)/D5</f>
+        <v>-0.37943696450428399</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <f>'xflr5 data'!C22</f>
+        <v>9.7699999999999992E-3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1.2359999999999999E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <f>(B6-D6)/D6</f>
+        <v>-0.20954692556634308</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <f>'xflr5 data'!C32</f>
+        <v>1.6209999999999999E-2</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2.1270000000000001E-2</v>
+      </c>
+      <c r="E7" s="4">
+        <f>(B7-D7)/D7</f>
+        <v>-0.23789374706158917</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>